--- a/Unity/Assets/Config/Excel/StartConfig/Release/StartMachineConfig.xlsx
+++ b/Unity/Assets/Config/Excel/StartConfig/Release/StartMachineConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12795"/>
+    <workbookView windowWidth="22188" windowHeight="9612"/>
   </bookViews>
   <sheets>
     <sheet name="StartMachineConfig" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
   <si>
     <t>##var</t>
   </si>
@@ -65,7 +65,10 @@
     <t>守护进程端口</t>
   </si>
   <si>
-    <t>127.0.0.1</t>
+    <t>192.168.53.105</t>
+  </si>
+  <si>
+    <t>115.190.237.40</t>
   </si>
 </sst>
 </file>
@@ -1066,11 +1069,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="3" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" outlineLevelRow="3" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="12.75" style="1" customWidth="1"/>
-    <col min="2" max="4" width="12.625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="13.9333333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6296296296296" style="2" customWidth="1"/>
+    <col min="3" max="3" width="16.6666666666667" style="2" customWidth="1"/>
+    <col min="4" max="4" width="16.2222222222222" style="2" customWidth="1"/>
+    <col min="5" max="5" width="13.9351851851852" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1133,7 +1138,7 @@
         <v>12</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" s="4">
         <v>10000</v>
